--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="347">
   <si>
     <t>50001591 - "ZITRON COLOMBIA  ARIS MARAMTO"</t>
   </si>
@@ -412,6 +412,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC Motor OT 4394,Fabricación Motor OT 4394 ,Planos motor proveedor OT 4394 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217117339188568</t>
@@ -3455,7 +3458,7 @@
         <v>46255.66337146991</v>
       </c>
       <c r="D34" s="5">
-        <v>46255.66338287037</v>
+        <v>46279.13492862269</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>123</v>
@@ -3499,8 +3502,8 @@
       <c r="R34" s="5">
         <v>46246</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>83</v>
+      <c r="S34" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T34" s="6">
         <v>1</v>
@@ -3511,7 +3514,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46237.58011546296</v>
@@ -3556,7 +3559,7 @@
         <v>44</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3566,7 +3569,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46237.580208009254</v>
@@ -3578,7 +3581,7 @@
         <v>46255.66335965278</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3611,7 +3614,7 @@
         <v>75</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3621,7 +3624,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="9">
         <v>46237.58026069445</v>
@@ -3633,7 +3636,7 @@
         <v>46255.66334568287</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3666,7 +3669,7 @@
         <v>75</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3676,7 +3679,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46237.570455486115</v>
@@ -3686,7 +3689,7 @@
         <v>46255.71529688657</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>25</v>
@@ -3710,7 +3713,7 @@
         <v>26</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3723,7 +3726,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="9">
         <v>46237.57046002315</v>
@@ -3735,16 +3738,16 @@
         <v>46252.60497945602</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I39" s="9">
         <v>46244</v>
@@ -3762,13 +3765,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>41</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q39" s="9">
         <v>46248</v>
@@ -3788,7 +3791,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46237.57046512731</v>
@@ -3800,16 +3803,16 @@
         <v>46273.15732342593</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I40" s="5">
         <v>46266</v>
@@ -3827,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>46272</v>
@@ -3853,7 +3856,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46237.57046940972</v>
@@ -3871,10 +3874,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46273</v>
@@ -3892,13 +3895,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="9">
         <v>46273</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46237.570483483796</v>
@@ -3928,16 +3931,16 @@
         <v>46239.60363896991</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46322</v>
@@ -3955,13 +3958,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q42" s="5">
         <v>46322</v>
@@ -3981,7 +3984,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="9">
         <v>46237.57048821759</v>
@@ -3991,16 +3994,16 @@
         <v>46239.63445903936</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="9">
         <v>46322</v>
@@ -4018,13 +4021,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46237.57049291667</v>
@@ -4044,16 +4047,16 @@
         <v>46239.63445802083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46322</v>
@@ -4071,13 +4074,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46237.57051701389</v>
@@ -4097,16 +4100,16 @@
         <v>46239.63445679398</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9">
         <v>46322</v>
@@ -4124,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4140,7 +4143,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46239.60363707176</v>
@@ -4150,16 +4153,16 @@
         <v>46239.65046148148</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I46" s="5">
         <v>46322</v>
@@ -4177,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4193,7 +4196,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="9">
         <v>46237.57052454861</v>
@@ -4203,7 +4206,7 @@
         <v>46237.796667546296</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4227,7 +4230,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46237.57052836806</v>
@@ -4250,16 +4253,16 @@
         <v>46239.57054138889</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I48" s="5">
         <v>46293</v>
@@ -4277,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46293</v>
@@ -4303,7 +4306,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46237.57053329861</v>
@@ -4313,16 +4316,16 @@
         <v>46239.570537754626</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I49" s="9">
         <v>46293</v>
@@ -4340,13 +4343,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>97</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q49" s="9">
         <v>46293</v>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46237.57053827547</v>
@@ -4376,16 +4379,16 @@
         <v>46239.570533715276</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I50" s="5">
         <v>46293</v>
@@ -4403,13 +4406,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46293</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46237.57054359953</v>
@@ -4439,7 +4442,7 @@
         <v>46239.570621273146</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4466,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9">
         <v>46294</v>
@@ -4492,7 +4495,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46237.570548668984</v>
@@ -4502,7 +4505,7 @@
         <v>46239.57061776621</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4529,13 +4532,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q52" s="5">
         <v>46294</v>
@@ -4555,7 +4558,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B53" s="9">
         <v>46237.57055390046</v>
@@ -4565,7 +4568,7 @@
         <v>46239.57061447916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4592,13 +4595,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9">
         <v>46294</v>
@@ -4618,7 +4621,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46237.57055873843</v>
@@ -4628,7 +4631,7 @@
         <v>46237.79991431713</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4652,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4665,7 +4668,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46237.570562442124</v>
@@ -4675,16 +4678,16 @@
         <v>46239.608869386575</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I55" s="9">
         <v>46295</v>
@@ -4702,13 +4705,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9">
         <v>46297</v>
@@ -4728,7 +4731,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46237.57056796296</v>
@@ -4738,16 +4741,16 @@
         <v>46239.603713460645</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46300</v>
@@ -4765,13 +4768,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56" s="5">
         <v>46304</v>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="9">
         <v>46237.57057246528</v>
@@ -4801,16 +4804,16 @@
         <v>46255.71530028935</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I57" s="9">
         <v>46300</v>
@@ -4828,13 +4831,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4844,7 +4847,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46237.570579224535</v>
@@ -4854,16 +4857,16 @@
         <v>46255.7152974537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I58" s="5">
         <v>46300</v>
@@ -4881,13 +4884,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4897,7 +4900,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46237.570585995374</v>
@@ -4907,16 +4910,16 @@
         <v>46255.715298125</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I59" s="9">
         <v>46300</v>
@@ -4934,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4950,7 +4953,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46239.60371085648</v>
@@ -4960,16 +4963,16 @@
         <v>46239.716654814816</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I60" s="5">
         <v>46300</v>
@@ -4987,13 +4990,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46237.57064327547</v>
@@ -5013,7 +5016,7 @@
         <v>46239.60380005787</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5038,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q61" s="9">
         <v>46307</v>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46237.570648796296</v>
@@ -5074,7 +5077,7 @@
         <v>46255.71530109954</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5101,13 +5104,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5117,7 +5120,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B63" s="9">
         <v>46237.57065361111</v>
@@ -5127,7 +5130,7 @@
         <v>46255.715298634255</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5154,13 +5157,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5170,7 +5173,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B64" s="5">
         <v>46237.57065883101</v>
@@ -5180,7 +5183,7 @@
         <v>46255.71529912037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5207,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5223,7 +5226,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
         <v>46239.60379768518</v>
@@ -5233,7 +5236,7 @@
         <v>46239.6206874537</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5258,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5274,7 +5277,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5">
         <v>46237.57067465278</v>
@@ -5284,7 +5287,7 @@
         <v>46237.80043872685</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5308,7 +5311,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5321,7 +5324,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B67" s="9">
         <v>46237.570677881944</v>
@@ -5331,16 +5334,16 @@
         <v>46242.17283251157</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I67" s="9">
         <v>46240</v>
@@ -5358,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>51</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q67" s="9">
         <v>46241</v>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
         <v>46237.57068269676</v>
@@ -5394,16 +5397,16 @@
         <v>46242.172833854165</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I68" s="5">
         <v>46240</v>
@@ -5421,13 +5424,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46241</v>
@@ -5447,7 +5450,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
         <v>46237.5706884838</v>
@@ -5457,16 +5460,16 @@
         <v>46255.66337329861</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I69" s="9">
         <v>46287</v>
@@ -5484,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46287</v>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46237.570694027774</v>
@@ -5520,7 +5523,7 @@
         <v>46237.808683634255</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5544,7 +5547,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5557,7 +5560,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="9">
         <v>46237.57069988426</v>
@@ -5567,7 +5570,7 @@
         <v>46239.61845846065</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5594,13 +5597,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="9">
         <v>46314</v>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46237.57070458333</v>
@@ -5630,7 +5633,7 @@
         <v>46239.57127634259</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5657,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="9">
         <v>46237.57070806713</v>
@@ -5683,7 +5686,7 @@
         <v>46239.57127222222</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5710,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5726,7 +5729,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46237.57071152778</v>
@@ -5736,7 +5739,7 @@
         <v>46239.57126841435</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5763,13 +5766,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5779,7 +5782,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B75" s="9">
         <v>46239.61845638889</v>
@@ -5789,7 +5792,7 @@
         <v>46239.620747719906</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5816,10 +5819,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>26</v>
@@ -5832,7 +5835,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" s="5">
         <v>46237.5792246412</v>
@@ -5842,7 +5845,7 @@
         <v>46239.6097567824</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5869,10 +5872,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5895,7 +5898,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B77" s="9">
         <v>46237.60174226852</v>
@@ -5905,7 +5908,7 @@
         <v>46239.571369108795</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5932,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5948,7 +5951,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46237.601752048606</v>
@@ -5958,7 +5961,7 @@
         <v>46239.57136590278</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5985,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6001,7 +6004,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46237.60176081018</v>
@@ -6011,7 +6014,7 @@
         <v>46239.571362627314</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6038,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" s="5">
         <v>46239.60975478009</v>
@@ -6064,7 +6067,7 @@
         <v>46239.64953579861</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B81" s="9">
         <v>46237.57076179398</v>
@@ -6117,7 +6120,7 @@
         <v>46239.60978591435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q81" s="9">
         <v>46316</v>
@@ -6170,7 +6173,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46237.570767337966</v>
@@ -6180,7 +6183,7 @@
         <v>46255.71529939814</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6207,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="9">
         <v>46237.57077200232</v>
@@ -6233,7 +6236,7 @@
         <v>46255.7152997338</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6260,13 +6263,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46237.570776238426</v>
@@ -6286,7 +6289,7 @@
         <v>46239.61779011574</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6313,13 +6316,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6329,7 +6332,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
         <v>46239.609783865744</v>
@@ -6339,7 +6342,7 @@
         <v>46239.617714872686</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6366,10 +6369,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6382,7 +6385,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46237.570741250005</v>
@@ -6392,7 +6395,7 @@
         <v>46239.60983028935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6419,13 +6422,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86" s="5">
         <v>46317</v>
@@ -6445,7 +6448,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B87" s="9">
         <v>46237.57074578704</v>
@@ -6455,7 +6458,7 @@
         <v>46239.57192630787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6482,13 +6485,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6498,7 +6501,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
         <v>46237.57074978009</v>
@@ -6508,7 +6511,7 @@
         <v>46239.57192538194</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6535,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6551,7 +6554,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
         <v>46237.570753935186</v>
@@ -6561,7 +6564,7 @@
         <v>46239.57192444445</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6588,13 +6591,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46239.6098277662</v>
@@ -6614,7 +6617,7 @@
         <v>46239.62314922454</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6641,10 +6644,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6657,7 +6660,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
         <v>46237.57069734954</v>
@@ -6667,7 +6670,7 @@
         <v>46239.60986582176</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6694,13 +6697,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q91" s="9">
         <v>46318</v>
@@ -6720,7 +6723,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
         <v>46237.60193265046</v>
@@ -6730,7 +6733,7 @@
         <v>46239.60990070602</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6757,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6773,7 +6776,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B93" s="9">
         <v>46237.601940740744</v>
@@ -6783,7 +6786,7 @@
         <v>46239.6099468287</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6810,13 +6813,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6826,7 +6829,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46237.60194800926</v>
@@ -6836,7 +6839,7 @@
         <v>46239.60997769676</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6863,13 +6866,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B95" s="9">
         <v>46239.609863680555</v>
@@ -6889,7 +6892,7 @@
         <v>46239.63397174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6916,10 +6919,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6932,7 +6935,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
         <v>46237.570830474535</v>
@@ -6942,7 +6945,7 @@
         <v>46239.61000172453</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6969,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="5">
         <v>46321</v>
@@ -6995,7 +6998,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B97" s="9">
         <v>46237.57083550926</v>
@@ -7005,7 +7008,7 @@
         <v>46239.572179930554</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7032,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7048,7 +7051,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B98" s="5">
         <v>46237.570847511575</v>
@@ -7058,7 +7061,7 @@
         <v>46239.57217587963</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7085,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B99" s="9">
         <v>46237.570855555554</v>
@@ -7111,7 +7114,7 @@
         <v>46239.57217159722</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7138,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7154,7 +7157,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B100" s="5">
         <v>46239.609999629625</v>
@@ -7164,7 +7167,7 @@
         <v>46239.634635740746</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7191,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7207,7 +7210,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B101" s="9">
         <v>46237.57086628472</v>
@@ -7217,7 +7220,7 @@
         <v>46239.610039652776</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7244,10 +7247,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>26</v>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B102" s="5">
         <v>46237.57087083333</v>
@@ -7280,7 +7283,7 @@
         <v>46239.63361798611</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7307,13 +7310,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7323,7 +7326,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B103" s="9">
         <v>46237.57087578704</v>
@@ -7333,7 +7336,7 @@
         <v>46239.63361701389</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7360,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B104" s="5">
         <v>46237.57088047454</v>
@@ -7386,7 +7389,7 @@
         <v>46239.63367186343</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7413,13 +7416,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7429,7 +7432,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B105" s="9">
         <v>46239.610037488426</v>
@@ -7439,7 +7442,7 @@
         <v>46239.65005603009</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7466,13 +7469,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7482,7 +7485,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B106" s="5">
         <v>46237.57088893518</v>
@@ -7492,7 +7495,7 @@
         <v>46237.81145841435</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>25</v>
@@ -7516,7 +7519,7 @@
         <v>26</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>26</v>
@@ -7529,7 +7532,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B107" s="9">
         <v>46237.570892731484</v>
@@ -7539,16 +7542,16 @@
         <v>46239.605107766205</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I107" s="9">
         <v>46324</v>
@@ -7566,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q107" s="9">
         <v>46324</v>
@@ -7592,7 +7595,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="5">
         <v>46237.57089802083</v>
@@ -7602,16 +7605,16 @@
         <v>46239.57251351852</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I108" s="5">
         <v>46324</v>
@@ -7629,13 +7632,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7645,7 +7648,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B109" s="9">
         <v>46237.570901921295</v>
@@ -7655,16 +7658,16 @@
         <v>46239.57250958333</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I109" s="9">
         <v>46324</v>
@@ -7682,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7698,7 +7701,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B110" s="5">
         <v>46237.570906064815</v>
@@ -7708,16 +7711,16 @@
         <v>46239.57250601852</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -7735,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B111" s="9">
         <v>46239.605104699076</v>
@@ -7761,16 +7764,16 @@
         <v>46239.65079266204</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I111" s="9">
         <v>46324</v>
@@ -7788,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7804,7 +7807,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B112" s="5">
         <v>46237.57091384259</v>
@@ -7814,7 +7817,7 @@
         <v>46239.60514053241</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7841,10 +7844,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -7867,7 +7870,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B113" s="9">
         <v>46237.570918125</v>
@@ -7877,7 +7880,7 @@
         <v>46239.57274636574</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7904,13 +7907,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B114" s="5">
         <v>46237.5709225</v>
@@ -7930,7 +7933,7 @@
         <v>46239.57274300926</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7957,13 +7960,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7973,7 +7976,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B115" s="9">
         <v>46237.57092643519</v>
@@ -7983,7 +7986,7 @@
         <v>46239.57273921296</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8010,13 +8013,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8026,7 +8029,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B116" s="5">
         <v>46239.60513822916</v>
@@ -8036,7 +8039,7 @@
         <v>46239.65121751158</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8061,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8077,7 +8080,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B117" s="9">
         <v>46237.5709340162</v>
@@ -8087,16 +8090,16 @@
         <v>46239.60517148148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I117" s="9">
         <v>46328</v>
@@ -8114,13 +8117,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q117" s="9">
         <v>46328</v>
@@ -8140,7 +8143,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B118" s="5">
         <v>46237.57093827546</v>
@@ -8150,16 +8153,16 @@
         <v>46239.57292194445</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I118" s="5">
         <v>46328</v>
@@ -8177,13 +8180,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8193,7 +8196,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B119" s="9">
         <v>46237.570942280094</v>
@@ -8203,16 +8206,16 @@
         <v>46239.57291828704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I119" s="9">
         <v>46328</v>
@@ -8230,13 +8233,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8246,7 +8249,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B120" s="5">
         <v>46237.570946203705</v>
@@ -8256,16 +8259,16 @@
         <v>46239.572914687495</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I120" s="5">
         <v>46328</v>
@@ -8283,13 +8286,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8299,7 +8302,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B121" s="9">
         <v>46239.60516900463</v>
@@ -8309,16 +8312,16 @@
         <v>46239.65163626157</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I121" s="9">
         <v>46328</v>
@@ -8336,13 +8339,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8352,7 +8355,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B122" s="5">
         <v>46237.57099806713</v>
@@ -8362,16 +8365,16 @@
         <v>46239.60520445602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I122" s="5">
         <v>46329</v>
@@ -8389,13 +8392,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q122" s="5">
         <v>46329</v>
@@ -8415,7 +8418,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B123" s="9">
         <v>46237.571004722224</v>
@@ -8425,16 +8428,16 @@
         <v>46239.573137245374</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I123" s="9">
         <v>46329</v>
@@ -8452,13 +8455,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8468,7 +8471,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B124" s="5">
         <v>46237.57100873842</v>
@@ -8478,16 +8481,16 @@
         <v>46239.57312887731</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I124" s="5">
         <v>46329</v>
@@ -8505,13 +8508,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8521,7 +8524,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B125" s="9">
         <v>46237.571012685185</v>
@@ -8531,16 +8534,16 @@
         <v>46239.57312516204</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I125" s="9">
         <v>46329</v>
@@ -8558,13 +8561,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8574,7 +8577,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B126" s="5">
         <v>46239.60520262731</v>
@@ -8584,16 +8587,16 @@
         <v>46239.65181268519</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I126" s="5">
         <v>46329</v>
@@ -8611,10 +8614,10 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -8627,7 +8630,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B127" s="9">
         <v>46237.571019675925</v>
@@ -8637,7 +8640,7 @@
         <v>46237.81196827546</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>25</v>
@@ -8661,7 +8664,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>26</v>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B128" s="5">
         <v>46237.571023171295</v>
@@ -8684,16 +8687,16 @@
         <v>46239.57346402778</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I128" s="5">
         <v>46331</v>
@@ -8711,13 +8714,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q128" s="5">
         <v>46339</v>
@@ -8737,7 +8740,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B129" s="9">
         <v>46237.57102857639</v>
@@ -8747,16 +8750,16 @@
         <v>46239.573531319445</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I129" s="9">
         <v>46331</v>
@@ -8774,13 +8777,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q129" s="9">
         <v>46339</v>

--- a/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
+++ b/data/50001591 - ZITRON COLOMBIA  ARIS MARAMTO.xlsx
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46239.569636203705</v>
+        <v>46280.16907614583</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46239.56972798611</v>
+        <v>46280.16907498843</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>67</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46239.56982333334</v>
+        <v>46280.169073576384</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>73</v>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46255.66337329861</v>
+        <v>46280.13613967593</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>226</v>
@@ -5501,8 +5501,8 @@
       <c r="R69" s="9">
         <v>46287</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>83</v>
+      <c r="S69" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
